--- a/campanas.xlsx
+++ b/campanas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pacificocia-my.sharepoint.com/personal/sergiocusicanquie_pacifico_com_pe/Documents/Proyectos DA PSalud - General/2. Data Science/Seguros Integrales/Sistema de recomendación/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pacificocia-my.sharepoint.com/personal/sanna_pamela_vidal_pacifico_com_pe/Documents/0Tranformacion/1 Squad Analítica Avanzada/3Prospeccion/Calculadora (Gidhub)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{9B1EC062-546A-4DAD-AB44-051D81297E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B8C787B-7002-49B9-A46F-6E447108F28F}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="8_{9B1EC062-546A-4DAD-AB44-051D81297E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{109B0936-925A-4D3D-B0E6-6129FE34E619}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A7EBDEC2-972C-4F61-A1FF-30EC84AC76B9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A7EBDEC2-972C-4F61-A1FF-30EC84AC76B9}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -27,16 +27,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
   <si>
     <t>Nombre</t>
   </si>
@@ -78,13 +79,16 @@
   </si>
   <si>
     <t>General</t>
+  </si>
+  <si>
+    <t>Campaña_Integrales2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -487,14 +491,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F8D576B-7000-4AA0-B166-0E5CDE4B32F9}">
-  <dimension ref="A1:K3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="24.7265625" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" customWidth="1"/>
+    <col min="1" max="1" width="24.69921875" customWidth="1"/>
+    <col min="2" max="2" width="15.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -529,7 +533,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -564,7 +568,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -597,6 +601,76 @@
       </c>
       <c r="K3">
         <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="2">
+        <v>46082</v>
+      </c>
+      <c r="D4" s="2">
+        <v>46172</v>
+      </c>
+      <c r="E4">
+        <v>23</v>
+      </c>
+      <c r="F4">
+        <v>23</v>
+      </c>
+      <c r="G4">
+        <v>31</v>
+      </c>
+      <c r="H4">
+        <v>23</v>
+      </c>
+      <c r="I4">
+        <v>31</v>
+      </c>
+      <c r="J4">
+        <v>23</v>
+      </c>
+      <c r="K4">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2">
+        <v>46082</v>
+      </c>
+      <c r="D5" s="2">
+        <v>46172</v>
+      </c>
+      <c r="E5">
+        <v>13</v>
+      </c>
+      <c r="F5">
+        <v>13</v>
+      </c>
+      <c r="G5">
+        <v>13</v>
+      </c>
+      <c r="H5">
+        <v>13</v>
+      </c>
+      <c r="I5">
+        <v>13</v>
+      </c>
+      <c r="J5">
+        <v>13</v>
+      </c>
+      <c r="K5">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/campanas.xlsx
+++ b/campanas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pacificocia-my.sharepoint.com/personal/sanna_pamela_vidal_pacifico_com_pe/Documents/0Tranformacion/1 Squad Analítica Avanzada/3Prospeccion/Calculadora (Gidhub)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="8_{9B1EC062-546A-4DAD-AB44-051D81297E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{109B0936-925A-4D3D-B0E6-6129FE34E619}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="8_{9B1EC062-546A-4DAD-AB44-051D81297E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3CAFB34-D9B5-4DC6-B0D6-1CA49226CCEF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A7EBDEC2-972C-4F61-A1FF-30EC84AC76B9}"/>
   </bookViews>
@@ -611,31 +611,31 @@
         <v>13</v>
       </c>
       <c r="C4" s="2">
-        <v>46082</v>
+        <v>46023</v>
       </c>
       <c r="D4" s="2">
         <v>46172</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I4">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J4">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K4">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -646,31 +646,31 @@
         <v>11</v>
       </c>
       <c r="C5" s="2">
-        <v>46082</v>
+        <v>46023</v>
       </c>
       <c r="D5" s="2">
         <v>46172</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K5">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/campanas.xlsx
+++ b/campanas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pacificocia-my.sharepoint.com/personal/sanna_pamela_vidal_pacifico_com_pe/Documents/0Tranformacion/1 Squad Analítica Avanzada/3Prospeccion/Calculadora (Gidhub)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="8_{9B1EC062-546A-4DAD-AB44-051D81297E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3CAFB34-D9B5-4DC6-B0D6-1CA49226CCEF}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="8_{9B1EC062-546A-4DAD-AB44-051D81297E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2ADE9851-6EAE-48E7-B879-FD17DD57D8A0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A7EBDEC2-972C-4F61-A1FF-30EC84AC76B9}"/>
   </bookViews>
@@ -81,7 +81,7 @@
     <t>General</t>
   </si>
   <si>
-    <t>Campaña_Integrales2</t>
+    <t>Campaña_Integrales</t>
   </si>
 </sst>
 </file>
@@ -611,10 +611,10 @@
         <v>13</v>
       </c>
       <c r="C4" s="2">
-        <v>46023</v>
+        <v>46113</v>
       </c>
       <c r="D4" s="2">
-        <v>46172</v>
+        <v>46142</v>
       </c>
       <c r="E4">
         <v>25</v>
@@ -646,10 +646,10 @@
         <v>11</v>
       </c>
       <c r="C5" s="2">
-        <v>46023</v>
+        <v>46113</v>
       </c>
       <c r="D5" s="2">
-        <v>46172</v>
+        <v>46142</v>
       </c>
       <c r="E5">
         <v>15</v>

--- a/campanas.xlsx
+++ b/campanas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pacificocia-my.sharepoint.com/personal/sanna_pamela_vidal_pacifico_com_pe/Documents/0Tranformacion/1 Squad Analítica Avanzada/3Prospeccion/Calculadora (Gidhub)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="8_{9B1EC062-546A-4DAD-AB44-051D81297E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2ADE9851-6EAE-48E7-B879-FD17DD57D8A0}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="8_{9B1EC062-546A-4DAD-AB44-051D81297E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABA5900E-A0E4-441F-848B-02858E3101A4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A7EBDEC2-972C-4F61-A1FF-30EC84AC76B9}"/>
   </bookViews>
@@ -614,7 +614,7 @@
         <v>46113</v>
       </c>
       <c r="D4" s="2">
-        <v>46142</v>
+        <v>46172</v>
       </c>
       <c r="E4">
         <v>25</v>
@@ -649,7 +649,7 @@
         <v>46113</v>
       </c>
       <c r="D5" s="2">
-        <v>46142</v>
+        <v>46172</v>
       </c>
       <c r="E5">
         <v>15</v>
